--- a/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
+++ b/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>20200424120000</t>
   </si>
   <si>
     <t>Name</t>

--- a/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
+++ b/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
@@ -81,7 +81,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
+++ b/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
@@ -7,7 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
-    <sheet name="Include from TRE-R247-UcumUni" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #0" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>

--- a/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
+++ b/ig/main/ValueSet-JDV-J37-UcumUniteTemps.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20200424120000</t>
+    <t>20240927120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2020-04-24T12:00:00+01:00</t>
+    <t>2024-09-27T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -159,7 +159,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R247-UcumUniteMesure/FHIR/TRE-R247-UcumUniteMesure</t>
+    <t>http://unitsofmeasure.org</t>
   </si>
 </sst>
 </file>
